--- a/artfynd/A 27290-2026 artfynd.xlsx
+++ b/artfynd/A 27290-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2924980</v>
+        <v>219408</v>
       </c>
       <c r="B2" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>106340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>400 m S Bränsle, Öl</t>
+          <t>700 m SSV Bränsle, Öl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>619044.6499145462</v>
+        <v>619017</v>
       </c>
       <c r="R2" t="n">
-        <v>6344044.652671915</v>
+        <v>6343854</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +752,9 @@
           <t>2010-08-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2010-08-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,27 +768,31 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Dikeskant</t>
+          <t>Lövglänta</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Wendt, Vera Wendt</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Vera Wendt, Göran Wendt</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>125404639</v>
       </c>
       <c r="B3" t="n">
-        <v>57597</v>
+        <v>57899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -900,6 +898,222 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2924980</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>400 m S Bränsle, Öl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>619045</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6344045</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2010-08-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2010-08-08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Dikeskant</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Vera Wendt, Göran Wendt</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>103178790</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kalmar län, Öl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>618948</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6343984</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>FC904885-91F7-4FC4-8B6F-628C3377E03F</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-12-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-12-18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>liggande skorsten</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Thomas Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27290-2026 artfynd.xlsx
+++ b/artfynd/A 27290-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/219408</t>
         </is>
       </c>
     </row>
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125404639</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2924980</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1113,8 +1133,19 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178790</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>